--- a/Figure 1/Mouse weight & GTT/WeightGTTBM.xlsx
+++ b/Figure 1/Mouse weight & GTT/WeightGTTBM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://api.box.com/wopi/files/1868134115757/WOPIServiceId_TP_BOX_2/WOPIUserId_-/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026-Human-Mice\Schoukroun-2026-Human-Mice\Figure 1\Mouse weight &amp; GTT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{8A183DEE-2B2F-421B-84B3-6F93119573B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7302666-6C93-48FE-90E1-BAB6BBE3E91A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACF78464-6D81-4DCE-95FA-2F7867570662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="2055" windowWidth="12690" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BM-Weight" sheetId="1" r:id="rId1"/>
@@ -123,9 +123,6 @@
     <t>BM5M2</t>
   </si>
   <si>
-    <t>BM4M3</t>
-  </si>
-  <si>
     <t>BM4M4</t>
   </si>
   <si>
@@ -148,6 +145,9 @@
   </si>
   <si>
     <t>BM2M5</t>
+  </si>
+  <si>
+    <t>BM4M5</t>
   </si>
 </sst>
 </file>
@@ -519,7 +519,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
@@ -536,7 +536,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>3</v>
@@ -553,7 +553,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>3</v>
@@ -587,7 +587,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>3</v>
@@ -672,7 +672,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
@@ -689,7 +689,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
@@ -706,7 +706,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
@@ -723,7 +723,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>3</v>
@@ -876,7 +876,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>3</v>
@@ -893,7 +893,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>3</v>
@@ -910,7 +910,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>3</v>
@@ -927,7 +927,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>3</v>
@@ -1012,7 +1012,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
@@ -1029,7 +1029,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
@@ -1046,7 +1046,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
@@ -1199,7 +1199,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>3</v>
@@ -1216,7 +1216,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>3</v>
@@ -1233,7 +1233,7 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>3</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>3</v>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>3</v>
@@ -1352,7 +1352,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>7</v>
@@ -1369,7 +1369,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>7</v>
@@ -1386,7 +1386,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>7</v>
@@ -1403,7 +1403,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>7</v>
@@ -1539,7 +1539,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>3</v>
@@ -1556,7 +1556,7 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>3</v>
@@ -1573,7 +1573,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>3</v>
@@ -1590,7 +1590,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>3</v>
@@ -1607,7 +1607,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>3</v>
@@ -1692,7 +1692,7 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>7</v>
@@ -1709,7 +1709,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>7</v>
@@ -1726,7 +1726,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>7</v>
@@ -1743,7 +1743,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>7</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>3</v>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>3</v>
@@ -1913,7 +1913,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>3</v>
@@ -1930,7 +1930,7 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>3</v>
@@ -1947,7 +1947,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>3</v>
@@ -2032,7 +2032,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>7</v>
@@ -2049,7 +2049,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>7</v>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>7</v>
@@ -2083,7 +2083,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>7</v>
@@ -2219,7 +2219,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>3</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>3</v>
@@ -2253,7 +2253,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>3</v>
@@ -2270,7 +2270,7 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>3</v>
@@ -2287,7 +2287,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>3</v>
@@ -2372,7 +2372,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>7</v>
@@ -2389,7 +2389,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>7</v>
@@ -2406,7 +2406,7 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>7</v>
@@ -2423,7 +2423,7 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>7</v>
@@ -2559,7 +2559,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>3</v>
@@ -2576,7 +2576,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>3</v>
@@ -2593,7 +2593,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>3</v>
@@ -2610,7 +2610,7 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>3</v>
@@ -2627,7 +2627,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>3</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>7</v>
@@ -2729,7 +2729,7 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>7</v>
@@ -2746,7 +2746,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>7</v>
@@ -2763,7 +2763,7 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>7</v>
@@ -2899,7 +2899,7 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>3</v>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>3</v>
@@ -2933,7 +2933,7 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>3</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>3</v>
@@ -2967,7 +2967,7 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>3</v>
@@ -3052,7 +3052,7 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>7</v>
@@ -3069,7 +3069,7 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>7</v>
@@ -3086,7 +3086,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>7</v>
@@ -3103,7 +3103,7 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>7</v>
@@ -3239,7 +3239,7 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>3</v>
@@ -3256,7 +3256,7 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>3</v>
@@ -3273,7 +3273,7 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>3</v>
@@ -3290,7 +3290,7 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>3</v>
@@ -3307,7 +3307,7 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>3</v>
@@ -3392,7 +3392,7 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>7</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>7</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>7</v>
@@ -3443,7 +3443,7 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>7</v>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>3</v>
@@ -3596,7 +3596,7 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>3</v>
@@ -3613,7 +3613,7 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>3</v>
@@ -3630,7 +3630,7 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>3</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>3</v>
@@ -3732,7 +3732,7 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>7</v>
@@ -3749,7 +3749,7 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>7</v>
@@ -3766,7 +3766,7 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>7</v>
@@ -3783,7 +3783,7 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>7</v>
@@ -3919,7 +3919,7 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>3</v>
@@ -3936,7 +3936,7 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>3</v>
@@ -3953,7 +3953,7 @@
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>3</v>
@@ -3970,7 +3970,7 @@
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>3</v>
@@ -3987,7 +3987,7 @@
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>3</v>
@@ -4072,7 +4072,7 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>7</v>
@@ -4089,7 +4089,7 @@
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>7</v>
@@ -4106,7 +4106,7 @@
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>7</v>
@@ -4123,7 +4123,7 @@
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>7</v>
@@ -4259,7 +4259,7 @@
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>3</v>
@@ -4276,7 +4276,7 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>3</v>
@@ -4293,7 +4293,7 @@
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>3</v>
@@ -4310,7 +4310,7 @@
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>3</v>
@@ -4327,7 +4327,7 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>3</v>
@@ -4412,7 +4412,7 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>7</v>
@@ -4429,7 +4429,7 @@
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>7</v>
@@ -4446,7 +4446,7 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>7</v>
@@ -4463,7 +4463,7 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>7</v>
@@ -4599,7 +4599,7 @@
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B242" s="1" t="s">
         <v>3</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>3</v>
@@ -4633,7 +4633,7 @@
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B244" s="1" t="s">
         <v>3</v>
@@ -4650,7 +4650,7 @@
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B245" s="1" t="s">
         <v>3</v>
@@ -4667,7 +4667,7 @@
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>3</v>
@@ -4752,7 +4752,7 @@
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>7</v>
@@ -4769,7 +4769,7 @@
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>7</v>
@@ -4786,7 +4786,7 @@
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>7</v>
@@ -4803,7 +4803,7 @@
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>7</v>
@@ -4939,7 +4939,7 @@
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B262" s="1" t="s">
         <v>3</v>
@@ -4956,7 +4956,7 @@
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B263" s="1" t="s">
         <v>3</v>
@@ -4973,7 +4973,7 @@
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>3</v>
@@ -4990,7 +4990,7 @@
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>3</v>
@@ -5007,7 +5007,7 @@
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>3</v>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>7</v>
@@ -5109,7 +5109,7 @@
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>7</v>
@@ -5126,7 +5126,7 @@
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>7</v>
@@ -5143,7 +5143,7 @@
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B274" s="1" t="s">
         <v>7</v>
@@ -5279,7 +5279,7 @@
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B282" s="1" t="s">
         <v>3</v>
@@ -5296,7 +5296,7 @@
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B283" s="1" t="s">
         <v>3</v>
@@ -5313,7 +5313,7 @@
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B284" s="1" t="s">
         <v>3</v>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>3</v>
@@ -5347,7 +5347,7 @@
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B286" s="1" t="s">
         <v>3</v>
@@ -5432,7 +5432,7 @@
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>7</v>
@@ -5449,7 +5449,7 @@
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B292" s="1" t="s">
         <v>7</v>
@@ -5466,7 +5466,7 @@
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B293" s="1" t="s">
         <v>7</v>
@@ -5483,7 +5483,7 @@
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B294" s="1" t="s">
         <v>7</v>
@@ -5619,7 +5619,7 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B302" s="1" t="s">
         <v>3</v>
@@ -5636,7 +5636,7 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B303" s="1" t="s">
         <v>3</v>
@@ -5653,7 +5653,7 @@
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B304" s="1" t="s">
         <v>3</v>
@@ -5670,7 +5670,7 @@
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B305" s="1" t="s">
         <v>3</v>
@@ -5687,7 +5687,7 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B306" s="1" t="s">
         <v>3</v>
@@ -5772,7 +5772,7 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B311" s="1" t="s">
         <v>7</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B312" s="1" t="s">
         <v>7</v>
@@ -5806,7 +5806,7 @@
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B313" s="1" t="s">
         <v>7</v>
@@ -5823,7 +5823,7 @@
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B314" s="1" t="s">
         <v>7</v>
@@ -5959,7 +5959,7 @@
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B322" s="1" t="s">
         <v>3</v>
@@ -5976,7 +5976,7 @@
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B323" s="1" t="s">
         <v>3</v>
@@ -5993,7 +5993,7 @@
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B324" s="1" t="s">
         <v>3</v>
@@ -6010,7 +6010,7 @@
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B325" s="1" t="s">
         <v>3</v>
@@ -6027,7 +6027,7 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B326" s="1" t="s">
         <v>3</v>
@@ -6112,7 +6112,7 @@
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B331" s="1" t="s">
         <v>7</v>
@@ -6129,7 +6129,7 @@
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B332" s="1" t="s">
         <v>7</v>
@@ -6146,7 +6146,7 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B333" s="1" t="s">
         <v>7</v>
@@ -6163,7 +6163,7 @@
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B334" s="1" t="s">
         <v>7</v>
@@ -6299,7 +6299,7 @@
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B342" s="1" t="s">
         <v>3</v>
@@ -6316,7 +6316,7 @@
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B343" s="1" t="s">
         <v>3</v>
@@ -6333,7 +6333,7 @@
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>3</v>
@@ -6350,7 +6350,7 @@
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>3</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B346" s="1" t="s">
         <v>3</v>
@@ -6452,7 +6452,7 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B351" s="1" t="s">
         <v>7</v>
@@ -6469,7 +6469,7 @@
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B352" s="1" t="s">
         <v>7</v>
@@ -6486,7 +6486,7 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B353" s="1" t="s">
         <v>7</v>
@@ -6503,7 +6503,7 @@
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B354" s="1" t="s">
         <v>7</v>
@@ -6639,7 +6639,7 @@
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B362" s="1" t="s">
         <v>3</v>
@@ -6656,7 +6656,7 @@
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B363" s="1" t="s">
         <v>3</v>
@@ -6673,7 +6673,7 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B364" s="1" t="s">
         <v>3</v>
@@ -6690,7 +6690,7 @@
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B365" s="1" t="s">
         <v>3</v>
@@ -6707,7 +6707,7 @@
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>3</v>
@@ -6792,7 +6792,7 @@
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B371" s="1" t="s">
         <v>7</v>
@@ -6809,7 +6809,7 @@
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B372" s="1" t="s">
         <v>7</v>
@@ -6826,7 +6826,7 @@
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B373" s="1" t="s">
         <v>7</v>
@@ -6843,7 +6843,7 @@
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B374" s="1" t="s">
         <v>7</v>
@@ -6979,7 +6979,7 @@
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B382" s="1" t="s">
         <v>3</v>
@@ -6996,7 +6996,7 @@
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B383" s="1" t="s">
         <v>3</v>
@@ -7013,7 +7013,7 @@
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B384" s="1" t="s">
         <v>3</v>
@@ -7030,7 +7030,7 @@
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B385" s="1" t="s">
         <v>3</v>
@@ -7047,7 +7047,7 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B386" s="1" t="s">
         <v>3</v>
@@ -7132,7 +7132,7 @@
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B391" s="1" t="s">
         <v>7</v>
@@ -7149,7 +7149,7 @@
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B392" s="1" t="s">
         <v>7</v>
@@ -7166,7 +7166,7 @@
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B393" s="1" t="s">
         <v>7</v>
@@ -7183,7 +7183,7 @@
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B394" s="1" t="s">
         <v>7</v>
@@ -7319,7 +7319,7 @@
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B402" s="1" t="s">
         <v>3</v>
@@ -7336,7 +7336,7 @@
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B403" s="1" t="s">
         <v>3</v>
@@ -7353,7 +7353,7 @@
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B404" s="1" t="s">
         <v>3</v>
@@ -7370,7 +7370,7 @@
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B405" s="1" t="s">
         <v>3</v>
@@ -7387,7 +7387,7 @@
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B406" s="1" t="s">
         <v>3</v>
@@ -7472,7 +7472,7 @@
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B411" s="1" t="s">
         <v>7</v>
@@ -7489,7 +7489,7 @@
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B412" s="1" t="s">
         <v>7</v>
@@ -7506,7 +7506,7 @@
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B413" s="1" t="s">
         <v>7</v>
@@ -7523,7 +7523,7 @@
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B414" s="1" t="s">
         <v>7</v>
@@ -7659,7 +7659,7 @@
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B422" s="1" t="s">
         <v>3</v>
@@ -7676,7 +7676,7 @@
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B423" s="1" t="s">
         <v>3</v>
@@ -7696,7 +7696,7 @@
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B424" s="1" t="s">
         <v>3</v>
@@ -7713,7 +7713,7 @@
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B425" s="1" t="s">
         <v>3</v>
@@ -7730,7 +7730,7 @@
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B426" s="1" t="s">
         <v>3</v>
@@ -7815,7 +7815,7 @@
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B431" s="1" t="s">
         <v>7</v>
@@ -7832,7 +7832,7 @@
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B432" s="1" t="s">
         <v>7</v>
@@ -7849,7 +7849,7 @@
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B433" s="1" t="s">
         <v>7</v>
@@ -7866,7 +7866,7 @@
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B434" s="1" t="s">
         <v>7</v>
@@ -8002,7 +8002,7 @@
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B442" s="1" t="s">
         <v>3</v>
@@ -8019,7 +8019,7 @@
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B443" s="1" t="s">
         <v>3</v>
@@ -8036,7 +8036,7 @@
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B444" s="1" t="s">
         <v>3</v>
@@ -8053,7 +8053,7 @@
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B445" s="1" t="s">
         <v>3</v>
@@ -8070,7 +8070,7 @@
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B446" s="1" t="s">
         <v>3</v>
@@ -8155,7 +8155,7 @@
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B451" s="1" t="s">
         <v>7</v>
@@ -8172,7 +8172,7 @@
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B452" s="1" t="s">
         <v>7</v>
@@ -8189,7 +8189,7 @@
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B453" s="1" t="s">
         <v>7</v>
@@ -8206,7 +8206,7 @@
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B454" s="1" t="s">
         <v>7</v>
@@ -8342,7 +8342,7 @@
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B462" s="1" t="s">
         <v>3</v>
@@ -8359,7 +8359,7 @@
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B463" s="1" t="s">
         <v>3</v>
@@ -8376,7 +8376,7 @@
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B464" s="1" t="s">
         <v>3</v>
@@ -8393,7 +8393,7 @@
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B465" s="1" t="s">
         <v>3</v>
@@ -8410,7 +8410,7 @@
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B466" s="1" t="s">
         <v>3</v>
@@ -8495,7 +8495,7 @@
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B471" s="1" t="s">
         <v>7</v>
@@ -8512,7 +8512,7 @@
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B472" s="1" t="s">
         <v>7</v>
@@ -8529,7 +8529,7 @@
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B473" s="1" t="s">
         <v>7</v>
@@ -8546,7 +8546,7 @@
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B474" s="1" t="s">
         <v>7</v>
@@ -8682,7 +8682,7 @@
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B482" s="1" t="s">
         <v>3</v>
@@ -8699,7 +8699,7 @@
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B483" s="1" t="s">
         <v>3</v>
@@ -8716,7 +8716,7 @@
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B484" s="1" t="s">
         <v>3</v>
@@ -8733,7 +8733,7 @@
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B485" s="1" t="s">
         <v>3</v>
@@ -8750,7 +8750,7 @@
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B486" s="1" t="s">
         <v>3</v>
@@ -8835,7 +8835,7 @@
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B491" s="1" t="s">
         <v>7</v>
@@ -8852,7 +8852,7 @@
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B492" s="1" t="s">
         <v>7</v>
@@ -8869,7 +8869,7 @@
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B493" s="1" t="s">
         <v>7</v>
@@ -8886,7 +8886,7 @@
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B494" s="1" t="s">
         <v>7</v>
@@ -9970,7 +9970,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B68" t="s">
         <v>4</v>
@@ -9984,7 +9984,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B69" t="s">
         <v>4</v>
@@ -9998,7 +9998,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B70" t="s">
         <v>4</v>
@@ -10012,7 +10012,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B71" t="s">
         <v>4</v>
@@ -10026,7 +10026,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B72" t="s">
         <v>4</v>
@@ -10040,7 +10040,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B73" t="s">
         <v>4</v>
@@ -10054,7 +10054,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B74" t="s">
         <v>4</v>
@@ -10068,7 +10068,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B75" t="s">
         <v>4</v>
@@ -10082,7 +10082,7 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B76" t="s">
         <v>4</v>
@@ -10096,7 +10096,7 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B77" t="s">
         <v>4</v>
@@ -10110,7 +10110,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B78" t="s">
         <v>4</v>
@@ -10124,7 +10124,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B79" t="s">
         <v>4</v>
@@ -10138,7 +10138,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B80" t="s">
         <v>4</v>
@@ -10152,7 +10152,7 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B81" t="s">
         <v>4</v>
@@ -10166,7 +10166,7 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B82" t="s">
         <v>4</v>
@@ -10180,7 +10180,7 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B83" t="s">
         <v>4</v>
@@ -10194,7 +10194,7 @@
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B84" t="s">
         <v>4</v>
@@ -10208,7 +10208,7 @@
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B85" t="s">
         <v>4</v>
@@ -10222,7 +10222,7 @@
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B86" t="s">
         <v>4</v>
@@ -10236,7 +10236,7 @@
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B87" t="s">
         <v>4</v>
@@ -10250,7 +10250,7 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B88" t="s">
         <v>4</v>
@@ -10264,7 +10264,7 @@
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B89" t="s">
         <v>4</v>
@@ -10278,7 +10278,7 @@
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B90" t="s">
         <v>4</v>
@@ -10292,7 +10292,7 @@
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B91" t="s">
         <v>4</v>
@@ -10306,7 +10306,7 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B92" t="s">
         <v>4</v>
@@ -10320,7 +10320,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B93" t="s">
         <v>4</v>
@@ -10334,7 +10334,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B94" t="s">
         <v>4</v>
@@ -10348,7 +10348,7 @@
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B95" t="s">
         <v>4</v>
@@ -10362,7 +10362,7 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B96" t="s">
         <v>4</v>
@@ -10376,7 +10376,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B97" t="s">
         <v>4</v>
@@ -10390,7 +10390,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B98" t="s">
         <v>4</v>
@@ -10404,7 +10404,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B99" t="s">
         <v>4</v>
@@ -10418,7 +10418,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B100" t="s">
         <v>4</v>
@@ -10432,7 +10432,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B101" t="s">
         <v>4</v>
@@ -10446,7 +10446,7 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B102" t="s">
         <v>4</v>
@@ -10460,7 +10460,7 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B103" t="s">
         <v>4</v>
@@ -10474,7 +10474,7 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B104" t="s">
         <v>4</v>
@@ -10488,7 +10488,7 @@
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B105" t="s">
         <v>4</v>
@@ -10502,7 +10502,7 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B106" t="s">
         <v>4</v>
@@ -10516,7 +10516,7 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B107" t="s">
         <v>4</v>
@@ -10530,7 +10530,7 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B108" t="s">
         <v>4</v>
@@ -10544,7 +10544,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B109" t="s">
         <v>4</v>
@@ -10558,7 +10558,7 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B110" t="s">
         <v>4</v>
@@ -10572,7 +10572,7 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B111" t="s">
         <v>4</v>
@@ -10586,7 +10586,7 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B112" t="s">
         <v>4</v>
@@ -10600,7 +10600,7 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B113" t="s">
         <v>4</v>
@@ -10614,7 +10614,7 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B114" t="s">
         <v>4</v>
@@ -10628,7 +10628,7 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B115" t="s">
         <v>4</v>
@@ -10642,7 +10642,7 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B116" t="s">
         <v>4</v>
@@ -10656,7 +10656,7 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B117" t="s">
         <v>4</v>
@@ -10670,7 +10670,7 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B118" t="s">
         <v>4</v>
@@ -10684,7 +10684,7 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B119" t="s">
         <v>4</v>
@@ -10698,7 +10698,7 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B120" t="s">
         <v>4</v>
@@ -10712,7 +10712,7 @@
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B121" t="s">
         <v>4</v>
